--- a/output/pdf_financials_xlsx/TBK.xlsx
+++ b/output/pdf_financials_xlsx/TBK.xlsx
@@ -4459,40 +4459,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>12.383078</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>12.832626</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>12.971946</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>15.117115</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>18.257999</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>18.370581</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>18.370581</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>18.801997</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>18.97129</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>18.945332</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>19.193288</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>19.182317</v>
       </c>
     </row>
     <row r="93">
@@ -5590,7 +5590,7 @@
         <v>-0.250085</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.347484</v>
+        <v>-1.622382</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>-6.497861</v>
@@ -7624,7 +7624,11 @@
           <t>Share-based payment reserves 8</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -9164,7 +9168,11 @@
           <t>Share‐based payment reserves 9</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -10288,7 +10296,11 @@
           <t>Share‐based payment reserves 12</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -11264,7 +11276,11 @@
           <t>Share-based payment reserves 10</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -12548,7 +12564,11 @@
           <t>Share-based payment reserves 11</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -12924,7 +12944,11 @@
           <t>Share-based payment reserve 8</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -13068,7 +13092,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" s="5" t="n">
         <v>12.383078</v>
       </c>
@@ -19538,7 +19566,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TBK.xlsx
+++ b/output/pdf_financials_xlsx/TBK.xlsx
@@ -879,40 +879,40 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.02372</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004901</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003005</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.024371</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.035935</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.035797</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.044301</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002399</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00065</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000307</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.027388</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002077</v>
       </c>
     </row>
     <row r="13">
@@ -1576,40 +1576,40 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-10.018537</v>
+        <v>-9.994816999999999</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.830197</v>
+        <v>-1.825296</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.269843</v>
+        <v>-1.266838</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-5.341128</v>
+        <v>-5.316757</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-4.09181</v>
+        <v>-4.055875</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>5.428902</v>
+        <v>5.464699</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.664322</v>
+        <v>-2.620021</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.271972</v>
+        <v>0.274371</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.388911</v>
+        <v>-0.388261</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.681817</v>
+        <v>-3.68151</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.402675</v>
+        <v>-0.375287</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.850005</v>
+        <v>-0.847928</v>
       </c>
     </row>
     <row r="28">
@@ -1662,40 +1662,40 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-10.018537</v>
+        <v>-9.994816999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.830197</v>
+        <v>-1.825296</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.269843</v>
+        <v>-1.266838</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.341128</v>
+        <v>-5.316757</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-4.09181</v>
+        <v>-4.055875</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>5.428902</v>
+        <v>5.464699</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.664322</v>
+        <v>-2.620021</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.271972</v>
+        <v>0.274371</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.388911</v>
+        <v>-0.388261</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.681817</v>
+        <v>-3.68151</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.402675</v>
+        <v>-0.375287</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.850005</v>
+        <v>-0.847928</v>
       </c>
     </row>
     <row r="30">
@@ -1910,19 +1910,19 @@
         <v>2.245407</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.359576</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.446605</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.436245</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.920113</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.801785</v>
       </c>
     </row>
     <row r="35">
@@ -1996,19 +1996,19 @@
         <v>2.245407</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.290932</v>
+        <v>1.650508</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.117004</v>
+        <v>0.563609</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.088741</v>
+        <v>1.524986</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.024415</v>
+        <v>1.944528</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.054188</v>
+        <v>0.855973</v>
       </c>
     </row>
     <row r="37">
@@ -2512,19 +2512,19 @@
         <v>0.027324</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.09303</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.344768</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.361926</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.934524</v>
+        <v>0.014411</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.814252</v>
+        <v>0.012467</v>
       </c>
     </row>
     <row r="49">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E204" s="5" t="n">
@@ -23282,7 +23282,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -27648,7 +27648,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">

--- a/output/pdf_financials_xlsx/TBK.xlsx
+++ b/output/pdf_financials_xlsx/TBK.xlsx
@@ -2153,25 +2153,25 @@
         <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.000469</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.000967</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.003394</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.008832</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.002241</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.001366</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -2196,25 +2196,25 @@
         <v>0.09458</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.035826</v>
+        <v>0.036295</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.07149899999999999</v>
+        <v>0.072466</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>0.103083</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.08628</v>
+        <v>0.089674</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.018288</v>
+        <v>0.02712</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.025522</v>
+        <v>0.027763</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.022472</v>
+        <v>0.023838</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0.018997</v>
@@ -2497,19 +2497,19 @@
         <v>0.09804</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.036854</v>
+        <v>0.036385</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.07567400000000001</v>
+        <v>0.074707</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.111543</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.040002</v>
+        <v>0.036608</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.027324</v>
+        <v>0.018492</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -4723,10 +4723,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-10.018537</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-1.830197</v>
@@ -4768,10 +4766,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -4813,10 +4809,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0.112106</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0.005973</v>
@@ -4858,10 +4852,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>0</v>
@@ -4903,10 +4895,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0.016446</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>-0.057531</v>
@@ -4948,10 +4938,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>-0.044172</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>-0.041473</v>
@@ -4993,10 +4981,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>0</v>
@@ -5038,10 +5024,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.08438</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>-0.093031</v>
@@ -5083,10 +5067,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.117562</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0.449548</v>
@@ -5128,10 +5110,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
@@ -5173,10 +5153,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>0</v>
@@ -5218,10 +5196,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -5230,16 +5206,16 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.0026</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.00312</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.003121</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.00312</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>0</v>
@@ -5263,28 +5239,26 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>-0.003544</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001474</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002476</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003728</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002119</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002071</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
@@ -5293,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002288</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
@@ -5308,10 +5282,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -5353,10 +5325,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -5398,10 +5368,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -5443,10 +5411,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -5467,19 +5433,19 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.156018</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.05435</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.014102</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.064385</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.007413</v>
       </c>
     </row>
     <row r="116">
@@ -5488,10 +5454,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -5533,10 +5497,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>0</v>
@@ -5578,10 +5540,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>9.452332999999999</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0.983423</v>
@@ -5623,10 +5583,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>-1.760903</v>
       </c>
       <c r="C119" s="3" t="n">
         <v>-0.868262</v>
@@ -5668,10 +5626,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -5713,10 +5669,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -5758,10 +5712,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>0</v>
@@ -5803,10 +5755,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -5848,10 +5798,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -5893,10 +5841,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -5938,10 +5884,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>0</v>
@@ -6050,10 +5994,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>0</v>
@@ -6095,10 +6037,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>2.637704</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>0.189305</v>
@@ -6207,10 +6147,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>0</v>
@@ -6252,10 +6190,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.516052</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>-1.167175</v>
@@ -6364,28 +6300,26 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>-0.003544</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001474</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002476</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003728</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002119</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002071</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
@@ -6394,7 +6328,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002288</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
@@ -6409,28 +6343,26 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.364293</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.488218</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.298878</v>
+        <v>-0.300352</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.856317</v>
+        <v>-0.858793</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-1.105729</v>
+        <v>-1.109457</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.549528</v>
+        <v>-0.551647</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.153496</v>
+        <v>-0.155567</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>-0.550401</v>
@@ -6439,7 +6371,7 @@
         <v>-0.559226</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-0.500088</v>
+        <v>-0.502376</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>-0.308946</v>
@@ -6459,7 +6391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P343"/>
+  <dimension ref="A1:P344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13175,10 +13107,8 @@
           <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E92" s="5" t="n">
+        <v>-10.018537</v>
       </c>
       <c r="F92" s="5" t="n">
         <v>-1.830197</v>
@@ -13243,10 +13173,8 @@
           <t>Amortization</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E93" s="5" t="n">
+        <v>0.003513</v>
       </c>
       <c r="F93" s="5" t="n">
         <v>0.002039</v>
@@ -13307,10 +13235,8 @@
           <t>StockBasedCompensation</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E94" s="5" t="n">
+        <v>0.117562</v>
       </c>
       <c r="F94" s="5" t="n">
         <v>0.449548</v>
@@ -13447,10 +13373,8 @@
           <t>NetOtherInvestingChanges</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E96" s="5" t="n">
+        <v>9.452332999999999</v>
       </c>
       <c r="F96" s="5" t="n">
         <v>0.983423</v>
@@ -13655,10 +13579,8 @@
           <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E99" s="5" t="n">
+        <v>0.016446</v>
       </c>
       <c r="F99" s="5" t="n">
         <v>-0.057531</v>
@@ -13719,10 +13641,8 @@
           <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E100" s="5" t="n">
+        <v>-0.044172</v>
       </c>
       <c r="F100" s="5" t="n">
         <v>-0.041473</v>
@@ -13853,10 +13773,8 @@
           <t>OperatingCashFlow</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E102" s="5" t="n">
+        <v>-0.360749</v>
       </c>
       <c r="F102" s="5" t="n">
         <v>-0.488218</v>
@@ -13976,7 +13894,11 @@
           <t>Net proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -14051,10 +13973,8 @@
           <t>InvestingCashFlow</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E105" s="5" t="n">
+        <v>-1.760903</v>
       </c>
       <c r="F105" s="5" t="n">
         <v>-0.868262</v>
@@ -14914,11 +14834,13 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>-0.003544</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -16498,7 +16420,11 @@
           <t>Net proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -17108,7 +17034,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -17865,10 +17795,8 @@
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E156" s="5" t="n">
+        <v>0.019678</v>
       </c>
       <c r="F156" s="5" t="n">
         <v>0.020218</v>
@@ -17933,10 +17861,8 @@
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E157" s="5" t="n">
+        <v>1.233266</v>
       </c>
       <c r="F157" s="5" t="n">
         <v>0.065551</v>
@@ -18005,10 +17931,8 @@
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E158" s="5" t="n">
+        <v>1.252944</v>
       </c>
       <c r="F158" s="5" t="n">
         <v>0.085769</v>
@@ -18072,7 +17996,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -18829,10 +18757,8 @@
           <t>FinancingCashFlow</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E169" s="5" t="n">
+        <v>2.637704</v>
       </c>
       <c r="F169" s="5" t="n">
         <v>0.189305</v>
@@ -18903,10 +18829,8 @@
           <t>ChangesInCash</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E170" s="5" t="n">
+        <v>0.516052</v>
       </c>
       <c r="F170" s="5" t="n">
         <v>-1.167175</v>
@@ -18973,10 +18897,8 @@
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E171" s="5" t="n">
+        <v>0.736892</v>
       </c>
       <c r="F171" s="5" t="n">
         <v>1.252944</v>
@@ -19041,10 +18963,8 @@
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E172" s="5" t="n">
+        <v>1.252944</v>
       </c>
       <c r="F172" s="5" t="n">
         <v>0.085769</v>
@@ -20253,10 +20173,8 @@
           <t>ChangeInReceivables</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E188" s="5" t="n">
+        <v>0.112106</v>
       </c>
       <c r="F188" s="5" t="n">
         <v>0.005973</v>
@@ -20401,10 +20319,8 @@
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E190" s="5" t="n">
+        <v>2.637704</v>
       </c>
       <c r="F190" s="5" t="n">
         <v>0.189305</v>
@@ -20473,10 +20389,8 @@
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E191" s="5" t="n">
+        <v>-0.101334</v>
       </c>
       <c r="F191" s="5" t="n">
         <v>-0.020928</v>
@@ -20547,10 +20461,8 @@
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E192" s="5" t="n">
+        <v>-1.656025</v>
       </c>
       <c r="F192" s="5" t="n">
         <v>-0.847334</v>
@@ -20683,33 +20595,25 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Non cash investing activities</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Amortization $</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Shares issued for mineral properties $</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" s="5" t="n">
+        <v>0.39722</v>
+      </c>
+      <c r="F194" s="5" t="n">
+        <v>0.074221</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -20736,20 +20640,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L194" s="5" t="n">
-        <v>0.000841</v>
-      </c>
-      <c r="M194" s="5" t="n">
-        <v>0.00041</v>
-      </c>
-      <c r="N194" s="5" t="n">
-        <v>0.00037</v>
-      </c>
-      <c r="O194" s="5" t="n">
-        <v>0.001071</v>
-      </c>
-      <c r="P194" s="5" t="n">
-        <v>0.000598</v>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="195">
@@ -20765,10 +20679,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Corporate development and communication</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
+          <t>Amortization $</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -20804,24 +20722,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L195" s="5" t="n">
+        <v>0.000841</v>
+      </c>
+      <c r="M195" s="5" t="n">
+        <v>0.00041</v>
       </c>
       <c r="N195" s="5" t="n">
-        <v>0.003</v>
+        <v>0.00037</v>
       </c>
       <c r="O195" s="5" t="n">
-        <v>0.014864</v>
+        <v>0.001071</v>
       </c>
       <c r="P195" s="5" t="n">
-        <v>0.04725</v>
+        <v>0.000598</v>
       </c>
     </row>
     <row r="196">
@@ -20837,14 +20751,10 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Listing and filing fees</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Corporate development and communication</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -20885,17 +20795,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M196" s="5" t="n">
-        <v>0.025764</v>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N196" s="5" t="n">
-        <v>0.123282</v>
+        <v>0.003</v>
       </c>
       <c r="O196" s="5" t="n">
-        <v>0.06575400000000001</v>
+        <v>0.014864</v>
       </c>
       <c r="P196" s="5" t="n">
-        <v>0.051567</v>
+        <v>0.04725</v>
       </c>
     </row>
     <row r="197">
@@ -20911,12 +20823,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Management fees 9</t>
+          <t>Listing and filing fees</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -20960,16 +20872,16 @@
         </is>
       </c>
       <c r="M197" s="5" t="n">
-        <v>0.1962</v>
+        <v>0.025764</v>
       </c>
       <c r="N197" s="5" t="n">
-        <v>0.162</v>
+        <v>0.123282</v>
       </c>
       <c r="O197" s="5" t="n">
-        <v>0.172057</v>
+        <v>0.06575400000000001</v>
       </c>
       <c r="P197" s="5" t="n">
-        <v>0.18</v>
+        <v>0.051567</v>
       </c>
     </row>
     <row r="198">
@@ -20985,7 +20897,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
+          <t>Management fees 9</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -21018,11 +20930,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J198" s="5" t="n">
-        <v>0.168576</v>
-      </c>
-      <c r="K198" s="5" t="n">
-        <v>0.07156800000000001</v>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -21030,16 +20946,16 @@
         </is>
       </c>
       <c r="M198" s="5" t="n">
-        <v>0.101578</v>
+        <v>0.1962</v>
       </c>
       <c r="N198" s="5" t="n">
-        <v>0.169453</v>
+        <v>0.162</v>
       </c>
       <c r="O198" s="5" t="n">
-        <v>0.130491</v>
+        <v>0.172057</v>
       </c>
       <c r="P198" s="5" t="n">
-        <v>0.1161</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="199">
@@ -21055,12 +20971,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Office and miscellaneous</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -21088,15 +21004,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J199" s="5" t="n">
+        <v>0.168576</v>
+      </c>
+      <c r="K199" s="5" t="n">
+        <v>0.07156800000000001</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -21104,16 +21016,16 @@
         </is>
       </c>
       <c r="M199" s="5" t="n">
-        <v>0.107701</v>
+        <v>0.101578</v>
       </c>
       <c r="N199" s="5" t="n">
-        <v>0.091858</v>
+        <v>0.169453</v>
       </c>
       <c r="O199" s="5" t="n">
-        <v>0.088116</v>
+        <v>0.130491</v>
       </c>
       <c r="P199" s="5" t="n">
-        <v>0.074979</v>
+        <v>0.1161</v>
       </c>
     </row>
     <row r="200">
@@ -21129,10 +21041,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Stock-based compensation 8/9</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -21173,23 +21089,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M200" s="5" t="n">
+        <v>0.107701</v>
+      </c>
+      <c r="N200" s="5" t="n">
+        <v>0.091858</v>
       </c>
       <c r="O200" s="5" t="n">
-        <v>0.315956</v>
-      </c>
-      <c r="P200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.088116</v>
+      </c>
+      <c r="P200" s="5" t="n">
+        <v>0.074979</v>
       </c>
     </row>
     <row r="201">
@@ -21205,31 +21115,39 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E201" s="5" t="n">
-        <v>0.586411</v>
-      </c>
-      <c r="F201" s="5" t="n">
-        <v>0.8496359999999999</v>
-      </c>
-      <c r="G201" s="5" t="n">
-        <v>0.665208</v>
-      </c>
-      <c r="H201" s="5" t="n">
-        <v>2.020951</v>
-      </c>
-      <c r="I201" s="5" t="n">
-        <v>4.266659</v>
-      </c>
-      <c r="J201" s="5" t="n">
-        <v>0.918539</v>
+          <t>Stock-based compensation 8/9</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
@@ -21241,17 +21159,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M201" s="5" t="n">
-        <v>0.617169</v>
-      </c>
-      <c r="N201" s="5" t="n">
-        <v>0.549963</v>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O201" s="5" t="n">
-        <v>0.788309</v>
-      </c>
-      <c r="P201" s="5" t="n">
-        <v>0.470494</v>
+        <v>0.315956</v>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="202">
@@ -21262,64 +21186,58 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Due diligence for mineral interests</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E202" s="5" t="n">
+        <v>0.586411</v>
+      </c>
+      <c r="F202" s="5" t="n">
+        <v>0.8496359999999999</v>
+      </c>
+      <c r="G202" s="5" t="n">
+        <v>0.665208</v>
+      </c>
+      <c r="H202" s="5" t="n">
+        <v>2.020951</v>
+      </c>
+      <c r="I202" s="5" t="n">
+        <v>4.266659</v>
+      </c>
+      <c r="J202" s="5" t="n">
+        <v>0.918539</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L202" s="5" t="n">
-        <v>0.052995</v>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M202" s="5" t="n">
-        <v>-0.02381</v>
+        <v>0.617169</v>
       </c>
       <c r="N202" s="5" t="n">
-        <v>0.019681</v>
+        <v>0.549963</v>
       </c>
       <c r="O202" s="5" t="n">
-        <v>0.06919599999999999</v>
+        <v>0.788309</v>
       </c>
       <c r="P202" s="5" t="n">
-        <v>0.01543</v>
+        <v>0.470494</v>
       </c>
     </row>
     <row r="203">
@@ -21335,14 +21253,10 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>ForeignExchangeTradingGains</t>
-        </is>
-      </c>
+          <t>Due diligence for mineral interests</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -21353,11 +21267,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G203" s="5" t="n">
-        <v>-0.013883</v>
-      </c>
-      <c r="H203" s="5" t="n">
-        <v>0.000829</v>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -21375,19 +21293,19 @@
         </is>
       </c>
       <c r="L203" s="5" t="n">
-        <v>4.9e-05</v>
+        <v>0.052995</v>
       </c>
       <c r="M203" s="5" t="n">
-        <v>-6.8e-05</v>
+        <v>-0.02381</v>
       </c>
       <c r="N203" s="5" t="n">
-        <v>5.9e-05</v>
+        <v>0.019681</v>
       </c>
       <c r="O203" s="5" t="n">
-        <v>-1.5e-05</v>
+        <v>0.06919599999999999</v>
       </c>
       <c r="P203" s="5" t="n">
-        <v>1.1e-05</v>
+        <v>0.01543</v>
       </c>
     </row>
     <row r="204">
@@ -21403,51 +21321,59 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Foreign exchange</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E204" s="5" t="n">
-        <v>-0.02372</v>
-      </c>
-      <c r="F204" s="5" t="n">
-        <v>-0.004901</v>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G204" s="5" t="n">
-        <v>-0.003005</v>
+        <v>-0.013883</v>
       </c>
       <c r="H204" s="5" t="n">
-        <v>-0.024371</v>
-      </c>
-      <c r="I204" s="5" t="n">
-        <v>-0.035935</v>
-      </c>
-      <c r="J204" s="5" t="n">
-        <v>-0.035797</v>
-      </c>
-      <c r="K204" s="5" t="n">
-        <v>-0.044301</v>
-      </c>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000829</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L204" s="5" t="n">
+        <v>4.9e-05</v>
       </c>
       <c r="M204" s="5" t="n">
-        <v>-0.00065</v>
+        <v>-6.8e-05</v>
       </c>
       <c r="N204" s="5" t="n">
-        <v>-0.000307</v>
+        <v>5.9e-05</v>
       </c>
       <c r="O204" s="5" t="n">
-        <v>-0.027388</v>
+        <v>-1.5e-05</v>
       </c>
       <c r="P204" s="5" t="n">
-        <v>-0.002077</v>
+        <v>1.1e-05</v>
       </c>
     </row>
     <row r="205">
@@ -21463,36 +21389,34 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 5</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E205" s="5" t="n">
-        <v>9.452332999999999</v>
+        <v>-0.02372</v>
       </c>
       <c r="F205" s="5" t="n">
-        <v>0.983423</v>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.004901</v>
+      </c>
+      <c r="G205" s="5" t="n">
+        <v>-0.003005</v>
+      </c>
+      <c r="H205" s="5" t="n">
+        <v>-0.024371</v>
       </c>
       <c r="I205" s="5" t="n">
-        <v>4.7e-05</v>
+        <v>-0.035935</v>
       </c>
       <c r="J205" s="5" t="n">
-        <v>0.11352</v>
-      </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.035797</v>
+      </c>
+      <c r="K205" s="5" t="n">
+        <v>-0.044301</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -21500,16 +21424,16 @@
         </is>
       </c>
       <c r="M205" s="5" t="n">
-        <v>0.116634</v>
+        <v>-0.00065</v>
       </c>
       <c r="N205" s="5" t="n">
-        <v>3.280692</v>
+        <v>-0.000307</v>
       </c>
       <c r="O205" s="5" t="n">
-        <v>0.006582</v>
+        <v>-0.027388</v>
       </c>
       <c r="P205" s="5" t="n">
-        <v>0.406803</v>
+        <v>-0.002077</v>
       </c>
     </row>
     <row r="206">
@@ -21525,19 +21449,15 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Expenditure on petroleum and natural gas properties</t>
+          <t>Impairment of exploration and evaluation assets 5</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E206" s="5" t="n">
+        <v>9.452332999999999</v>
+      </c>
+      <c r="F206" s="5" t="n">
+        <v>0.983423</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -21549,15 +21469,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I206" s="5" t="n">
+        <v>4.7e-05</v>
+      </c>
+      <c r="J206" s="5" t="n">
+        <v>0.11352</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
@@ -21570,16 +21486,16 @@
         </is>
       </c>
       <c r="M206" s="5" t="n">
-        <v>0.026014</v>
+        <v>0.116634</v>
       </c>
       <c r="N206" s="5" t="n">
-        <v>0.02155</v>
+        <v>3.280692</v>
       </c>
       <c r="O206" s="5" t="n">
-        <v>0.020319</v>
+        <v>0.006582</v>
       </c>
       <c r="P206" s="5" t="n">
-        <v>0.019017</v>
+        <v>0.406803</v>
       </c>
     </row>
     <row r="207">
@@ -21595,7 +21511,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Miscellaneous income 5</t>
+          <t>Expenditure on petroleum and natural gas properties</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -21639,19 +21555,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M207" s="5" t="n">
+        <v>0.026014</v>
       </c>
       <c r="N207" s="5" t="n">
-        <v>-0.08325100000000001</v>
+        <v>0.02155</v>
       </c>
       <c r="O207" s="5" t="n">
-        <v>-0.07872800000000001</v>
+        <v>0.020319</v>
       </c>
       <c r="P207" s="5" t="n">
-        <v>-0.007125</v>
+        <v>0.019017</v>
       </c>
     </row>
     <row r="208">
@@ -21667,7 +21581,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Royalty income</t>
+          <t>Miscellaneous income 5</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -21686,14 +21600,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H208" s="5" t="n">
-        <v>-0.0138</v>
-      </c>
-      <c r="I208" s="5" t="n">
-        <v>-0.015</v>
-      </c>
-      <c r="J208" s="5" t="n">
-        <v>-0.025039</v>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
@@ -21705,17 +21625,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M208" s="5" t="n">
-        <v>-0.023165</v>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N208" s="5" t="n">
-        <v>-0.02825</v>
+        <v>-0.08325100000000001</v>
       </c>
       <c r="O208" s="5" t="n">
-        <v>-0.026452</v>
+        <v>-0.07872800000000001</v>
       </c>
       <c r="P208" s="5" t="n">
-        <v>-0.009195999999999999</v>
+        <v>-0.007125</v>
       </c>
     </row>
     <row r="209">
@@ -21731,7 +21653,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Settlement of flow-through share premium 8</t>
+          <t>Royalty income</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -21750,20 +21672,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H209" s="5" t="n">
+        <v>-0.0138</v>
+      </c>
+      <c r="I209" s="5" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="J209" s="5" t="n">
+        <v>-0.025039</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
@@ -21775,19 +21691,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M209" s="5" t="n">
+        <v>-0.023165</v>
       </c>
       <c r="N209" s="5" t="n">
-        <v>-0.08432000000000001</v>
+        <v>-0.02825</v>
       </c>
       <c r="O209" s="5" t="n">
-        <v>-0.349148</v>
+        <v>-0.026452</v>
       </c>
       <c r="P209" s="5" t="n">
-        <v>-0.043352</v>
+        <v>-0.009195999999999999</v>
       </c>
     </row>
     <row r="210">
@@ -21803,14 +21717,10 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Total other income (expenses)</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Settlement of flow-through share premium 8</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -21851,17 +21761,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M210" s="5" t="n">
-        <v>0.228258</v>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N210" s="5" t="n">
-        <v>-3.131854</v>
+        <v>-0.08432000000000001</v>
       </c>
       <c r="O210" s="5" t="n">
-        <v>0.385634</v>
+        <v>-0.349148</v>
       </c>
       <c r="P210" s="5" t="n">
-        <v>-0.379511</v>
+        <v>-0.043352</v>
       </c>
     </row>
     <row r="211">
@@ -21877,12 +21789,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Net loss $</t>
+          <t>Total other income (expenses)</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -21926,16 +21838,16 @@
         </is>
       </c>
       <c r="M211" s="5" t="n">
-        <v>-0.388911</v>
+        <v>0.228258</v>
       </c>
       <c r="N211" s="5" t="n">
-        <v>-3.681817</v>
+        <v>-3.131854</v>
       </c>
       <c r="O211" s="5" t="n">
-        <v>-0.402675</v>
+        <v>0.385634</v>
       </c>
       <c r="P211" s="5" t="n">
-        <v>-0.850005</v>
+        <v>-0.379511</v>
       </c>
     </row>
     <row r="212">
@@ -21946,15 +21858,19 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>FVTOCI, net of tax 6</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr"/>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -21996,16 +21912,16 @@
         </is>
       </c>
       <c r="M212" s="5" t="n">
-        <v>-0.119578</v>
+        <v>-0.388911</v>
       </c>
       <c r="N212" s="5" t="n">
-        <v>-0.046411</v>
+        <v>-3.681817</v>
       </c>
       <c r="O212" s="5" t="n">
-        <v>-0.009741</v>
+        <v>-0.402675</v>
       </c>
       <c r="P212" s="5" t="n">
-        <v>0.030061</v>
+        <v>-0.850005</v>
       </c>
     </row>
     <row r="213">
@@ -22021,14 +21937,10 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>FVTOCI, net of tax 6</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -22070,16 +21982,16 @@
         </is>
       </c>
       <c r="M213" s="5" t="n">
-        <v>-0.508489</v>
+        <v>-0.119578</v>
       </c>
       <c r="N213" s="5" t="n">
-        <v>-3.728228</v>
+        <v>-0.046411</v>
       </c>
       <c r="O213" s="5" t="n">
-        <v>-0.412416</v>
+        <v>-0.009741</v>
       </c>
       <c r="P213" s="5" t="n">
-        <v>-0.819944</v>
+        <v>0.030061</v>
       </c>
     </row>
     <row r="214">
@@ -22095,12 +22007,12 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted $</t>
+          <t>Comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -22144,16 +22056,16 @@
         </is>
       </c>
       <c r="M214" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-0.508489</v>
       </c>
       <c r="N214" s="5" t="n">
-        <v>-1.4e-07</v>
+        <v>-3.728228</v>
       </c>
       <c r="O214" s="5" t="n">
-        <v>1e-08</v>
+        <v>-0.412416</v>
       </c>
       <c r="P214" s="5" t="n">
-        <v>-2e-08</v>
+        <v>-0.819944</v>
       </c>
     </row>
     <row r="215">
@@ -22164,31 +22076,43 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding, basic and diluted</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
+          <t>Loss per share, basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F215" s="5" t="n">
-        <v>72.912873</v>
-      </c>
-      <c r="G215" s="5" t="n">
-        <v>99.804965</v>
-      </c>
-      <c r="H215" s="5" t="n">
-        <v>129.342152</v>
-      </c>
-      <c r="I215" s="5" t="n">
-        <v>183.49457</v>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -22200,20 +22124,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L215" s="5" t="n">
-        <v>11.537593</v>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M215" s="5" t="n">
-        <v>12.643364</v>
+        <v>-3e-08</v>
       </c>
       <c r="N215" s="5" t="n">
-        <v>25.666</v>
+        <v>-1.4e-07</v>
       </c>
       <c r="O215" s="5" t="n">
-        <v>38.804688</v>
+        <v>1e-08</v>
       </c>
       <c r="P215" s="5" t="n">
-        <v>40.654973</v>
+        <v>-2e-08</v>
       </c>
     </row>
     <row r="216">
@@ -22224,12 +22150,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Decommissioning Expenses</t>
+          <t>Weighted average number of common shares outstanding, basic and diluted</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -22238,25 +22164,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F216" s="5" t="n">
+        <v>72.912873</v>
+      </c>
+      <c r="G216" s="5" t="n">
+        <v>99.804965</v>
+      </c>
+      <c r="H216" s="5" t="n">
+        <v>129.342152</v>
+      </c>
+      <c r="I216" s="5" t="n">
+        <v>183.49457</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -22268,28 +22186,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L216" s="5" t="n">
+        <v>11.537593</v>
+      </c>
+      <c r="M216" s="5" t="n">
+        <v>12.643364</v>
       </c>
       <c r="N216" s="5" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="O216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>25.666</v>
+      </c>
+      <c r="O216" s="5" t="n">
+        <v>38.804688</v>
+      </c>
+      <c r="P216" s="5" t="n">
+        <v>40.654973</v>
       </c>
     </row>
     <row r="217">
@@ -22300,52 +22210,62 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Investor relations</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E217" s="5" t="n">
-        <v>0.046771</v>
-      </c>
-      <c r="F217" s="5" t="n">
-        <v>0.013681</v>
-      </c>
-      <c r="G217" s="5" t="n">
-        <v>0.004385</v>
-      </c>
-      <c r="H217" s="5" t="n">
-        <v>0.023781</v>
-      </c>
-      <c r="I217" s="5" t="n">
-        <v>0.023714</v>
-      </c>
-      <c r="J217" s="5" t="n">
-        <v>0.01995</v>
-      </c>
-      <c r="K217" s="5" t="n">
-        <v>0.0025</v>
+          <t>Decommissioning Expenses</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M217" s="5" t="n">
-        <v>0.016223</v>
-      </c>
-      <c r="N217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N217" s="5" t="n">
+        <v>0.006</v>
       </c>
       <c r="O217" t="inlineStr">
         <is>
@@ -22371,44 +22291,34 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Stock-based compensation 8,9</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E218" s="5" t="n">
+        <v>0.046771</v>
+      </c>
+      <c r="F218" s="5" t="n">
+        <v>0.013681</v>
+      </c>
+      <c r="G218" s="5" t="n">
+        <v>0.004385</v>
+      </c>
+      <c r="H218" s="5" t="n">
+        <v>0.023781</v>
+      </c>
+      <c r="I218" s="5" t="n">
+        <v>0.023714</v>
+      </c>
+      <c r="J218" s="5" t="n">
+        <v>0.01995</v>
+      </c>
+      <c r="K218" s="5" t="n">
+        <v>0.0025</v>
       </c>
       <c r="L218" t="inlineStr">
         <is>
@@ -22416,7 +22326,7 @@
         </is>
       </c>
       <c r="M218" s="5" t="n">
-        <v>0.169293</v>
+        <v>0.016223</v>
       </c>
       <c r="N218" t="inlineStr">
         <is>
@@ -22442,12 +22352,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Income from government grant</t>
+          <t>Stock-based compensation 8,9</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -22492,7 +22402,7 @@
         </is>
       </c>
       <c r="M219" s="5" t="n">
-        <v>-0.018431</v>
+        <v>0.169293</v>
       </c>
       <c r="N219" t="inlineStr">
         <is>
@@ -22523,7 +22433,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Miscellaneous income</t>
+          <t>Income from government grant</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -22568,10 +22478,12 @@
         </is>
       </c>
       <c r="M220" s="5" t="n">
-        <v>-0.304782</v>
-      </c>
-      <c r="N220" s="5" t="n">
-        <v>-0.08325100000000001</v>
+        <v>-0.018431</v>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O220" t="inlineStr">
         <is>
@@ -22597,7 +22509,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Settlement of flow-through share premium</t>
+          <t>Miscellaneous income</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -22641,13 +22553,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M221" s="5" t="n">
+        <v>-0.304782</v>
       </c>
       <c r="N221" s="5" t="n">
-        <v>-0.08432000000000001</v>
+        <v>-0.08325100000000001</v>
       </c>
       <c r="O221" t="inlineStr">
         <is>
@@ -22668,20 +22578,24 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding,</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding, basic and diluted</t>
+          <t>Settlement of flow-through share premium</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
-      <c r="E222" s="5" t="n">
-        <v>67.21353999999999</v>
-      </c>
-      <c r="F222" s="5" t="n">
-        <v>72.912873</v>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -22713,11 +22627,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M222" s="5" t="n">
-        <v>12.643364</v>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N222" s="5" t="n">
-        <v>25.666</v>
+        <v>-0.08432000000000001</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -22738,28 +22654,20 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Corporate development and communication              10                                       ‐             2,400</t>
+          <t>Weighted average number of common shares outstanding,</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Listing and filing fees</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Weighted average number of common shares outstanding, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" s="5" t="n">
+        <v>67.21353999999999</v>
+      </c>
+      <c r="F223" s="5" t="n">
+        <v>72.912873</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -22786,16 +22694,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L223" s="5" t="n">
-        <v>0.027254</v>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M223" s="5" t="n">
-        <v>0.025764</v>
-      </c>
-      <c r="N223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>12.643364</v>
+      </c>
+      <c r="N223" s="5" t="n">
+        <v>25.666</v>
       </c>
       <c r="O223" t="inlineStr">
         <is>
@@ -22821,12 +22729,12 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Management fees 10</t>
+          <t>Listing and filing fees</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -22865,10 +22773,10 @@
         </is>
       </c>
       <c r="L224" s="5" t="n">
-        <v>0.20775</v>
+        <v>0.027254</v>
       </c>
       <c r="M224" s="5" t="n">
-        <v>0.1962</v>
+        <v>0.025764</v>
       </c>
       <c r="N224" t="inlineStr">
         <is>
@@ -22894,12 +22802,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Investor relations                                                              16,223                          ‐</t>
+          <t>Corporate development and communication              10                                       ‐             2,400</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
+          <t>Management fees 10</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -22943,10 +22851,10 @@
         </is>
       </c>
       <c r="L225" s="5" t="n">
-        <v>0.137982</v>
+        <v>0.20775</v>
       </c>
       <c r="M225" s="5" t="n">
-        <v>0.101578</v>
+        <v>0.1962</v>
       </c>
       <c r="N225" t="inlineStr">
         <is>
@@ -22977,12 +22885,12 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Office and miscellaneous</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -23021,10 +22929,10 @@
         </is>
       </c>
       <c r="L226" s="5" t="n">
-        <v>0.169774</v>
+        <v>0.137982</v>
       </c>
       <c r="M226" s="5" t="n">
-        <v>0.107701</v>
+        <v>0.101578</v>
       </c>
       <c r="N226" t="inlineStr">
         <is>
@@ -23050,15 +22958,19 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Rent                                                                                                                       ‐             (2,519)</t>
+          <t>Investor relations                                                              16,223                          ‐</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Stock‐based compensation 9,10</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -23095,10 +23007,10 @@
         </is>
       </c>
       <c r="L227" s="5" t="n">
-        <v>0.090016</v>
+        <v>0.169774</v>
       </c>
       <c r="M227" s="5" t="n">
-        <v>0.169293</v>
+        <v>0.107701</v>
       </c>
       <c r="N227" t="inlineStr">
         <is>
@@ -23129,7 +23041,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Rent                                                                                                                       ‐             (2,519) total</t>
+          <t>Stock‐based compensation 9,10</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -23169,10 +23081,10 @@
         </is>
       </c>
       <c r="L228" s="5" t="n">
-        <v>-0.633498</v>
+        <v>0.090016</v>
       </c>
       <c r="M228" s="5" t="n">
-        <v>-0.617169</v>
+        <v>0.169293</v>
       </c>
       <c r="N228" t="inlineStr">
         <is>
@@ -23198,12 +23110,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Gain from disposal of wells                                7,12                                      ‐          (269,863)</t>
+          <t>Rent                                                                                                                       ‐             (2,519)</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Income from government grant 16</t>
+          <t>Rent                                                                                                                       ‐             (2,519) total</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -23243,10 +23155,10 @@
         </is>
       </c>
       <c r="L229" s="5" t="n">
-        <v>-0.1</v>
+        <v>-0.633498</v>
       </c>
       <c r="M229" s="5" t="n">
-        <v>-0.018431</v>
+        <v>-0.617169</v>
       </c>
       <c r="N229" t="inlineStr">
         <is>
@@ -23277,14 +23189,10 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Income from government grant 16</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -23321,10 +23229,10 @@
         </is>
       </c>
       <c r="L230" s="5" t="n">
-        <v>-0.002399</v>
+        <v>-0.1</v>
       </c>
       <c r="M230" s="5" t="n">
-        <v>-0.00065</v>
+        <v>-0.018431</v>
       </c>
       <c r="N230" t="inlineStr">
         <is>
@@ -23355,10 +23263,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 5</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -23395,10 +23307,10 @@
         </is>
       </c>
       <c r="L231" s="5" t="n">
-        <v>0.032606</v>
+        <v>-0.002399</v>
       </c>
       <c r="M231" s="5" t="n">
-        <v>0.116634</v>
+        <v>-0.00065</v>
       </c>
       <c r="N231" t="inlineStr">
         <is>
@@ -23429,7 +23341,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Expenditures on petroleum and natural gas properties 7</t>
+          <t>Impairment of exploration and evaluation assets 5</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -23469,10 +23381,10 @@
         </is>
       </c>
       <c r="L232" s="5" t="n">
-        <v>0.045691</v>
+        <v>0.032606</v>
       </c>
       <c r="M232" s="5" t="n">
-        <v>0.026014</v>
+        <v>0.116634</v>
       </c>
       <c r="N232" t="inlineStr">
         <is>
@@ -23503,7 +23415,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Miscellaneous income 6</t>
+          <t>Expenditures on petroleum and natural gas properties 7</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -23543,10 +23455,10 @@
         </is>
       </c>
       <c r="L233" s="5" t="n">
-        <v>-0.186304</v>
+        <v>0.045691</v>
       </c>
       <c r="M233" s="5" t="n">
-        <v>-0.304782</v>
+        <v>0.026014</v>
       </c>
       <c r="N233" t="inlineStr">
         <is>
@@ -23572,12 +23484,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Revaluation of decommissioning liabilities                                                                     ‐          (209,855)</t>
+          <t>Gain from disposal of wells                                7,12                                      ‐          (269,863)</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Royalty income</t>
+          <t>Miscellaneous income 6</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -23617,10 +23529,10 @@
         </is>
       </c>
       <c r="L234" s="5" t="n">
-        <v>-0.02583</v>
+        <v>-0.186304</v>
       </c>
       <c r="M234" s="5" t="n">
-        <v>-0.023165</v>
+        <v>-0.304782</v>
       </c>
       <c r="N234" t="inlineStr">
         <is>
@@ -23646,19 +23558,15 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Settlement of flow‐through share premium                                                                    ‐          (242,560)</t>
+          <t>Revaluation of decommissioning liabilities                                                                     ‐          (209,855)</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Total other income</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Royalty income</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -23695,10 +23603,10 @@
         </is>
       </c>
       <c r="L235" s="5" t="n">
-        <v>0.90547</v>
+        <v>-0.02583</v>
       </c>
       <c r="M235" s="5" t="n">
-        <v>0.228258</v>
+        <v>-0.023165</v>
       </c>
       <c r="N235" t="inlineStr">
         <is>
@@ -23729,12 +23637,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Net (loss) income $</t>
+          <t>Total other income</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -23773,10 +23681,10 @@
         </is>
       </c>
       <c r="L236" s="5" t="n">
-        <v>0.271972</v>
+        <v>0.90547</v>
       </c>
       <c r="M236" s="5" t="n">
-        <v>-0.388911</v>
+        <v>0.228258</v>
       </c>
       <c r="N236" t="inlineStr">
         <is>
@@ -23802,15 +23710,19 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Other comprehensive (loss) income</t>
+          <t>Settlement of flow‐through share premium                                                                    ‐          (242,560)</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>FVTOCI, net of tax 6</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>Net (loss) income $</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -23847,10 +23759,10 @@
         </is>
       </c>
       <c r="L237" s="5" t="n">
-        <v>0.001433</v>
+        <v>0.271972</v>
       </c>
       <c r="M237" s="5" t="n">
-        <v>-0.119578</v>
+        <v>-0.388911</v>
       </c>
       <c r="N237" t="inlineStr">
         <is>
@@ -23881,7 +23793,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Comprehensive (loss) income for the year $</t>
+          <t>FVTOCI, net of tax 6</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -23921,10 +23833,10 @@
         </is>
       </c>
       <c r="L238" s="5" t="n">
-        <v>0.273405</v>
+        <v>0.001433</v>
       </c>
       <c r="M238" s="5" t="n">
-        <v>-0.508489</v>
+        <v>-0.119578</v>
       </c>
       <c r="N238" t="inlineStr">
         <is>
@@ -23955,14 +23867,10 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Income (loss) per share, basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Comprehensive (loss) income for the year $</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -23999,10 +23907,10 @@
         </is>
       </c>
       <c r="L239" s="5" t="n">
-        <v>2e-08</v>
+        <v>0.273405</v>
       </c>
       <c r="M239" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-0.508489</v>
       </c>
       <c r="N239" t="inlineStr">
         <is>
@@ -24028,15 +23936,19 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Other comprehensive (loss) income</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Total 4,898,473 47,450 169,293 (508,489) 4,606,727 Total 3,781,119 996,493 (242,560) ‐ 90,016</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>Income (loss) per share, basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -24073,10 +23985,10 @@
         </is>
       </c>
       <c r="L240" s="5" t="n">
-        <v>4.898473</v>
+        <v>2e-08</v>
       </c>
       <c r="M240" s="5" t="n">
-        <v>0.273405</v>
+        <v>-3e-08</v>
       </c>
       <c r="N240" t="inlineStr">
         <is>
@@ -24102,12 +24014,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>‐ ‐            ‐ ‐ ‐ ‐</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>(388,911) 271,972 Deficit Deficit (64,318,692) (64,707,603)</t>
+          <t>Total 4,898,473 47,450 169,293 (508,489) 4,606,727 Total 3,781,119 996,493 (242,560) ‐ 90,016</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -24147,10 +24059,10 @@
         </is>
       </c>
       <c r="L241" s="5" t="n">
-        <v>-64.318692</v>
+        <v>4.898473</v>
       </c>
       <c r="M241" s="5" t="n">
-        <v>-64.590664</v>
+        <v>0.273405</v>
       </c>
       <c r="N241" t="inlineStr">
         <is>
@@ -24176,49 +24088,55 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>‐ ‐            ‐ ‐ ‐ ‐</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Listing and filing fees $</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E242" s="5" t="n">
-        <v>0.023402</v>
-      </c>
-      <c r="F242" s="5" t="n">
-        <v>0.025554</v>
-      </c>
-      <c r="G242" s="5" t="n">
-        <v>0.026501</v>
-      </c>
-      <c r="H242" s="5" t="n">
-        <v>0.04278</v>
-      </c>
-      <c r="I242" s="5" t="n">
-        <v>0.055955</v>
-      </c>
-      <c r="J242" s="5" t="n">
-        <v>0.035987</v>
-      </c>
-      <c r="K242" s="5" t="n">
-        <v>0.025439</v>
-      </c>
-      <c r="L242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>(388,911) 271,972 Deficit Deficit (64,318,692) (64,707,603)</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L242" s="5" t="n">
+        <v>-64.318692</v>
+      </c>
+      <c r="M242" s="5" t="n">
+        <v>-64.590664</v>
       </c>
       <c r="N242" t="inlineStr">
         <is>
@@ -24249,40 +24167,34 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Management consulting 13</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Listing and filing fees $</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E243" s="5" t="n">
+        <v>0.023402</v>
+      </c>
+      <c r="F243" s="5" t="n">
+        <v>0.025554</v>
+      </c>
+      <c r="G243" s="5" t="n">
+        <v>0.026501</v>
+      </c>
+      <c r="H243" s="5" t="n">
+        <v>0.04278</v>
+      </c>
+      <c r="I243" s="5" t="n">
+        <v>0.055955</v>
       </c>
       <c r="J243" s="5" t="n">
-        <v>0.1477</v>
+        <v>0.035987</v>
       </c>
       <c r="K243" s="5" t="n">
-        <v>0.03335</v>
+        <v>0.025439</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -24323,7 +24235,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Corporate development and communication 13</t>
+          <t>Management consulting 13</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -24353,10 +24265,10 @@
         </is>
       </c>
       <c r="J244" s="5" t="n">
-        <v>0.088648</v>
+        <v>0.1477</v>
       </c>
       <c r="K244" s="5" t="n">
-        <v>0.061892</v>
+        <v>0.03335</v>
       </c>
       <c r="L244" t="inlineStr">
         <is>
@@ -24397,14 +24309,10 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Professional fees 13</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Corporate development and communication 13</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -24431,10 +24339,10 @@
         </is>
       </c>
       <c r="J245" s="5" t="n">
-        <v>0.303665</v>
+        <v>0.088648</v>
       </c>
       <c r="K245" s="5" t="n">
-        <v>0.09688099999999999</v>
+        <v>0.061892</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -24475,12 +24383,12 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Professional fees 13</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -24509,10 +24417,10 @@
         </is>
       </c>
       <c r="J246" s="5" t="n">
-        <v>0.03831</v>
+        <v>0.303665</v>
       </c>
       <c r="K246" s="5" t="n">
-        <v>0.04751</v>
+        <v>0.09688099999999999</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
@@ -24553,10 +24461,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Accretion 15</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -24583,10 +24495,10 @@
         </is>
       </c>
       <c r="J247" s="5" t="n">
-        <v>0.003121</v>
+        <v>0.03831</v>
       </c>
       <c r="K247" s="5" t="n">
-        <v>0.00312</v>
+        <v>0.04751</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
@@ -24622,12 +24534,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Stock‐based compensation                      12                                     ‐                112,582</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Stock‐based compensation                      12                                     ‐                112,582 total</t>
+          <t>Accretion 15</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
@@ -24657,10 +24569,10 @@
         </is>
       </c>
       <c r="J248" s="5" t="n">
-        <v>-0.918539</v>
+        <v>0.003121</v>
       </c>
       <c r="K248" s="5" t="n">
-        <v>-0.34226</v>
+        <v>0.00312</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -24696,12 +24608,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Rental income                                                             (82,237)                                   ‐</t>
+          <t>Stock‐based compensation                      12                                     ‐                112,582</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Royalty income</t>
+          <t>Stock‐based compensation                      12                                     ‐                112,582 total</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -24731,10 +24643,10 @@
         </is>
       </c>
       <c r="J249" s="5" t="n">
-        <v>-0.025039</v>
+        <v>-0.918539</v>
       </c>
       <c r="K249" s="5" t="n">
-        <v>-0.024568</v>
+        <v>-0.34226</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -24775,14 +24687,10 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Royalty income</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -24809,10 +24717,10 @@
         </is>
       </c>
       <c r="J250" s="5" t="n">
-        <v>0.00278</v>
+        <v>-0.025039</v>
       </c>
       <c r="K250" s="5" t="n">
-        <v>0.062748</v>
+        <v>-0.024568</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -24853,12 +24761,12 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Foreign Exchange</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>ForeignExchangeTradingGains</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -24887,10 +24795,10 @@
         </is>
       </c>
       <c r="J251" s="5" t="n">
-        <v>-0.071909</v>
+        <v>0.00278</v>
       </c>
       <c r="K251" s="5" t="n">
-        <v>-0.000904</v>
+        <v>0.062748</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
@@ -24926,15 +24834,19 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Fair value adjustment on investment               9                  1,516,043                                   ‐</t>
+          <t>Rental income                                                             (82,237)                                   ‐</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Loss on equity accounted investment 9</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr"/>
+          <t>Foreign Exchange</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -24961,10 +24873,10 @@
         </is>
       </c>
       <c r="J252" s="5" t="n">
-        <v>0.456516</v>
+        <v>-0.071909</v>
       </c>
       <c r="K252" s="5" t="n">
-        <v>0.123275</v>
+        <v>-0.000904</v>
       </c>
       <c r="L252" t="inlineStr">
         <is>
@@ -25000,12 +24912,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Adjustment to accrued liabilities                                                                       ‐                   3,159</t>
+          <t>Fair value adjustment on investment               9                  1,516,043                                   ‐</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Adjustment to accrued liabilities                                                                       ‐                   3,159 total</t>
+          <t>Loss on equity accounted investment 9</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -25035,10 +24947,10 @@
         </is>
       </c>
       <c r="J253" s="5" t="n">
-        <v>6.347441</v>
+        <v>0.456516</v>
       </c>
       <c r="K253" s="5" t="n">
-        <v>-2.322062</v>
+        <v>0.123275</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
@@ -25079,14 +24991,10 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Net income (loss)</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Adjustment to accrued liabilities                                                                       ‐                   3,159 total</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -25113,10 +25021,10 @@
         </is>
       </c>
       <c r="J254" s="5" t="n">
-        <v>5.428902</v>
+        <v>6.347441</v>
       </c>
       <c r="K254" s="5" t="n">
-        <v>-2.664322</v>
+        <v>-2.322062</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -25152,12 +25060,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>securities                                     9                    (20,833)                                   ‐</t>
+          <t>Adjustment to accrued liabilities                                                                       ‐                   3,159</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) for the year $</t>
+          <t>Net income (loss)</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -25194,7 +25102,7 @@
         <v>5.428902</v>
       </c>
       <c r="K255" s="5" t="n">
-        <v>-2.685155</v>
+        <v>-2.664322</v>
       </c>
       <c r="L255" t="inlineStr">
         <is>
@@ -25235,12 +25143,12 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Earnings (loss) per share, basic $</t>
+          <t>Comprehensive income (loss) for the year $</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -25269,10 +25177,10 @@
         </is>
       </c>
       <c r="J256" s="5" t="n">
-        <v>5.699999999999999e-07</v>
+        <v>5.428902</v>
       </c>
       <c r="K256" s="5" t="n">
-        <v>-2.8e-07</v>
+        <v>-2.685155</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -25308,17 +25216,17 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>securities                                     9                    (20,833)                                   ‐</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding, basic</t>
+          <t>Earnings (loss) per share, basic $</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -25341,14 +25249,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I257" s="5" t="n">
-        <v>183.49457</v>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J257" s="5" t="n">
-        <v>9.517150000000001</v>
+        <v>5.699999999999999e-07</v>
       </c>
       <c r="K257" s="5" t="n">
-        <v>9.517150000000001</v>
+        <v>-2.8e-07</v>
       </c>
       <c r="L257" t="inlineStr">
         <is>
@@ -25389,12 +25299,12 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Earnings (loss) per share, diluted $</t>
+          <t>Weighted average number of common shares outstanding, basic</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>DilutedEPS</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -25417,16 +25327,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I258" s="5" t="n">
+        <v>183.49457</v>
       </c>
       <c r="J258" s="5" t="n">
-        <v>5.2e-07</v>
+        <v>9.517150000000001</v>
       </c>
       <c r="K258" s="5" t="n">
-        <v>-2.8e-07</v>
+        <v>9.517150000000001</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -25467,12 +25375,12 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding, diluted</t>
+          <t>Earnings (loss) per share, diluted $</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>DilutedAverageShares</t>
+          <t>DilutedEPS</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -25495,14 +25403,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I259" s="5" t="n">
-        <v>183.49457</v>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J259" s="5" t="n">
-        <v>10.345106</v>
+        <v>5.2e-07</v>
       </c>
       <c r="K259" s="5" t="n">
-        <v>9.517150000000001</v>
+        <v>-2.8e-07</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -25543,10 +25453,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>5,428,902 112,582 Total 14,992,923 (2,685,155) 12,307,768 Total 19,439,598</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding, diluted</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -25567,16 +25481,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I260" s="5" t="n">
+        <v>183.49457</v>
       </c>
       <c r="J260" s="5" t="n">
-        <v>14.992923</v>
+        <v>10.345106</v>
       </c>
       <c r="K260" s="5" t="n">
-        <v>-9.988159</v>
+        <v>9.517150000000001</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -25617,7 +25529,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>(2,664,322) 5,428,902 (9,988,159) ‐ Deficit (53,110,626) (55,774,948) Deficit</t>
+          <t>5,428,902 112,582 Total 14,992,923 (2,685,155) 12,307,768 Total 19,439,598</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
@@ -25647,10 +25559,10 @@
         </is>
       </c>
       <c r="J261" s="5" t="n">
-        <v>-53.110626</v>
+        <v>14.992923</v>
       </c>
       <c r="K261" s="5" t="n">
-        <v>-48.551369</v>
+        <v>-9.988159</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -25686,12 +25598,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>‐            ‐ ‐ ‐</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Reserve 1,195,608 1,195,608 Reserve</t>
+          <t>(2,664,322) 5,428,902 (9,988,159) ‐ Deficit (53,110,626) (55,774,948) Deficit</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -25721,10 +25633,10 @@
         </is>
       </c>
       <c r="J262" s="5" t="n">
-        <v>1.195608</v>
+        <v>-53.110626</v>
       </c>
       <c r="K262" s="5" t="n">
-        <v>1.195608</v>
+        <v>-48.551369</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -25760,12 +25672,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>‐            ‐ ‐ ‐</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Management consulting 11</t>
+          <t>Reserve 1,195,608 1,195,608 Reserve</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
@@ -25784,19 +25696,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H263" s="5" t="n">
-        <v>0.059691</v>
-      </c>
-      <c r="I263" s="5" t="n">
-        <v>0.075</v>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J263" s="5" t="n">
-        <v>0.1477</v>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.195608</v>
+      </c>
+      <c r="K263" s="5" t="n">
+        <v>1.195608</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -25837,7 +25751,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Bonus</t>
+          <t>Management consulting 11</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -25856,18 +25770,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H264" s="5" t="n">
+        <v>0.059691</v>
       </c>
       <c r="I264" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.075</v>
+      </c>
+      <c r="J264" s="5" t="n">
+        <v>0.1477</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
@@ -25913,14 +25823,10 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -25931,8 +25837,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G265" s="5" t="n">
-        <v>0.06</v>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -25940,7 +25848,7 @@
         </is>
       </c>
       <c r="I265" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.3</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -25991,10 +25899,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Corporate development and communication 11</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr"/>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -26005,19 +25917,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H266" s="5" t="n">
-        <v>0.056935</v>
+      <c r="G266" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I266" s="5" t="n">
-        <v>0.089555</v>
-      </c>
-      <c r="J266" s="5" t="n">
-        <v>0.088648</v>
+        <v>0.0015</v>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
@@ -26063,14 +25977,10 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Office and miscellaneous 11</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Corporate development and communication 11</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -26087,13 +25997,13 @@
         </is>
       </c>
       <c r="H267" s="5" t="n">
-        <v>0.148932</v>
+        <v>0.056935</v>
       </c>
       <c r="I267" s="5" t="n">
-        <v>0.142756</v>
+        <v>0.089555</v>
       </c>
       <c r="J267" s="5" t="n">
-        <v>0.168576</v>
+        <v>0.088648</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
@@ -26139,12 +26049,12 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Professional fees 11</t>
+          <t>Office and miscellaneous 11</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -26163,13 +26073,13 @@
         </is>
       </c>
       <c r="H268" s="5" t="n">
-        <v>0.427974</v>
+        <v>0.148932</v>
       </c>
       <c r="I268" s="5" t="n">
-        <v>0.341625</v>
+        <v>0.142756</v>
       </c>
       <c r="J268" s="5" t="n">
-        <v>0.303665</v>
+        <v>0.168576</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
@@ -26215,12 +26125,12 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Rent 11</t>
+          <t>Professional fees 11</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -26239,13 +26149,13 @@
         </is>
       </c>
       <c r="H269" s="5" t="n">
-        <v>0.07425</v>
+        <v>0.427974</v>
       </c>
       <c r="I269" s="5" t="n">
-        <v>0.0396</v>
+        <v>0.341625</v>
       </c>
       <c r="J269" s="5" t="n">
-        <v>0.03831</v>
+        <v>0.303665</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
@@ -26291,10 +26201,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Accretion 12</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
+          <t>Rent 11</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -26310,16 +26224,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H270" s="5" t="n">
+        <v>0.07425</v>
       </c>
       <c r="I270" s="5" t="n">
-        <v>0.00312</v>
+        <v>0.0396</v>
       </c>
       <c r="J270" s="5" t="n">
-        <v>0.003121</v>
+        <v>0.03831</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
@@ -26365,7 +26277,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Stock-based compensation 10</t>
+          <t>Accretion 12</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -26384,14 +26296,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H271" s="5" t="n">
-        <v>1.184008</v>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I271" s="5" t="n">
-        <v>3.193834</v>
+        <v>0.00312</v>
       </c>
       <c r="J271" s="5" t="n">
-        <v>0.112582</v>
+        <v>0.003121</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
@@ -26432,19 +26346,15 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Stock-based compensation 10</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -26460,16 +26370,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H272" s="5" t="n">
+        <v>1.184008</v>
       </c>
       <c r="I272" s="5" t="n">
-        <v>0.002651</v>
+        <v>3.193834</v>
       </c>
       <c r="J272" s="5" t="n">
-        <v>0.00278</v>
+        <v>0.112582</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
@@ -26515,12 +26423,12 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Foreign Exchange</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>ForeignExchangeTradingGains</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -26544,10 +26452,10 @@
         </is>
       </c>
       <c r="I273" s="5" t="n">
-        <v>0.10098</v>
+        <v>0.002651</v>
       </c>
       <c r="J273" s="5" t="n">
-        <v>-0.071909</v>
+        <v>0.00278</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
@@ -26593,10 +26501,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Gain on disposal of well-site equipment</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
+          <t>Foreign Exchange</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -26618,12 +26530,10 @@
         </is>
       </c>
       <c r="I274" s="5" t="n">
-        <v>-0.025845</v>
-      </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.10098</v>
+      </c>
+      <c r="J274" s="5" t="n">
+        <v>-0.071909</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
@@ -26669,7 +26579,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Gain from distribution as per arrangement 6</t>
+          <t>Gain on disposal of well-site equipment</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
@@ -26693,13 +26603,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J275" s="5" t="n">
-        <v>-6.790671</v>
+      <c r="I275" s="5" t="n">
+        <v>-0.025845</v>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
@@ -26745,7 +26655,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Loss on equity accounted investment 7</t>
+          <t>Gain from distribution as per arrangement 6</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
@@ -26775,7 +26685,7 @@
         </is>
       </c>
       <c r="J276" s="5" t="n">
-        <v>0.456516</v>
+        <v>-6.790671</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
@@ -26821,7 +26731,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Adjustment to accrued liabilities</t>
+          <t>Loss on equity accounted investment 7</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
@@ -26845,11 +26755,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I277" s="5" t="n">
-        <v>-0.201747</v>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J277" s="5" t="n">
-        <v>0.003159</v>
+        <v>0.456516</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
@@ -26895,27 +26807,35 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Other items total</t>
+          <t>Adjustment to accrued liabilities</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
-      <c r="E278" s="5" t="n">
-        <v>-9.432126</v>
-      </c>
-      <c r="F278" s="5" t="n">
-        <v>-0.980561</v>
-      </c>
-      <c r="G278" s="5" t="n">
-        <v>-0.609633</v>
-      </c>
-      <c r="H278" s="5" t="n">
-        <v>-3.322777</v>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I278" s="5" t="n">
-        <v>0.174849</v>
+        <v>-0.201747</v>
       </c>
       <c r="J278" s="5" t="n">
-        <v>6.337441</v>
+        <v>0.003159</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -26961,39 +26881,27 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Net and comprehensive income (loss) for the year $</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Other items total</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" s="5" t="n">
+        <v>-9.432126</v>
+      </c>
+      <c r="F279" s="5" t="n">
+        <v>-0.980561</v>
+      </c>
+      <c r="G279" s="5" t="n">
+        <v>-0.609633</v>
+      </c>
+      <c r="H279" s="5" t="n">
+        <v>-3.322777</v>
       </c>
       <c r="I279" s="5" t="n">
-        <v>-4.09181</v>
+        <v>0.174849</v>
       </c>
       <c r="J279" s="5" t="n">
-        <v>5.428902</v>
+        <v>6.337441</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -27039,12 +26947,12 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Income (loss) per share, basic $</t>
+          <t>Net and comprehensive income (loss) for the year $</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -27068,10 +26976,10 @@
         </is>
       </c>
       <c r="I280" s="5" t="n">
-        <v>-2e-08</v>
+        <v>-4.09181</v>
       </c>
       <c r="J280" s="5" t="n">
-        <v>3e-08</v>
+        <v>5.428902</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -27112,17 +27020,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Income (loss) per share, diluted $</t>
+          <t>Income (loss) per share, basic $</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>DilutedEPS</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -27195,10 +27103,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>5,428,902 112,582 5,976,112 1,037,863 62,500 3,193,834 6 Total 19,439,598 (9,988,159) 14,992,923 Total 13,261,099</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr"/>
+          <t>Income (loss) per share, diluted $</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -27220,10 +27132,10 @@
         </is>
       </c>
       <c r="I282" s="5" t="n">
-        <v>19.439598</v>
+        <v>-2e-08</v>
       </c>
       <c r="J282" s="5" t="n">
-        <v>-4.09181</v>
+        <v>3e-08</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
@@ -27269,7 +27181,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Deficit (48,551,369) 5,428,902 (9,988,159) (53,110,626) Deficit (44,459,559) (4,091,810) - - -</t>
+          <t>5,428,902 112,582 5,976,112 1,037,863 62,500 3,193,834 6 Total 19,439,598 (9,988,159) 14,992,923 Total 13,261,099</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -27294,12 +27206,10 @@
         </is>
       </c>
       <c r="I283" s="5" t="n">
-        <v>-48.551369</v>
-      </c>
-      <c r="J283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>19.439598</v>
+      </c>
+      <c r="J283" s="5" t="n">
+        <v>-4.09181</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -27340,12 +27250,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>- - -         -   - - -                                                                                                                                                                                                                                                                                                                                                                                                                                   financial</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Reserve 1,195,608 1,195,608 Reserve</t>
+          <t>Deficit (48,551,369) 5,428,902 (9,988,159) (53,110,626) Deficit (44,459,559) (4,091,810) - - -</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -27370,10 +27280,12 @@
         </is>
       </c>
       <c r="I284" s="5" t="n">
-        <v>1.195608</v>
-      </c>
-      <c r="J284" s="5" t="n">
-        <v>1.195608</v>
+        <v>-48.551369</v>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
@@ -27414,12 +27326,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>$      $     $         $                                                            capital                                                                                      capital</t>
+          <t>- - -         -   - - -                                                                                                                                                                                                                                                                                                                                                                                                                                   financial</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Share shares - - - Share shares - - of of 8,889,572 1,125,000 accompanying 190,343,723 190,343,723 167,623,436</t>
+          <t>Reserve 1,195,608 1,195,608 Reserve</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -27444,10 +27356,10 @@
         </is>
       </c>
       <c r="I285" s="5" t="n">
-        <v>190.343723</v>
+        <v>1.195608</v>
       </c>
       <c r="J285" s="5" t="n">
-        <v>12.705715</v>
+        <v>1.195608</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -27488,12 +27400,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>$      $     $         $                                                            capital                                                                                      capital</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Bonus 11</t>
+          <t>Share shares - - - Share shares - - of of 8,889,572 1,125,000 accompanying 190,343,723 190,343,723 167,623,436</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -27518,12 +27430,10 @@
         </is>
       </c>
       <c r="I286" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>190.343723</v>
+      </c>
+      <c r="J286" s="5" t="n">
+        <v>12.705715</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
@@ -27569,7 +27479,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Accretion 13</t>
+          <t>Bonus 11</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -27588,11 +27498,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H287" s="5" t="n">
-        <v>0.0026</v>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I287" s="5" t="n">
-        <v>0.00312</v>
+        <v>0.3</v>
       </c>
       <c r="J287" t="inlineStr">
         <is>
@@ -27638,19 +27550,15 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Accretion 13</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -27667,10 +27575,10 @@
         </is>
       </c>
       <c r="H288" s="5" t="n">
-        <v>-0.024371</v>
+        <v>0.0026</v>
       </c>
       <c r="I288" s="5" t="n">
-        <v>-0.035935</v>
+        <v>0.00312</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
@@ -27721,10 +27629,14 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Royalty income</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -27741,10 +27653,10 @@
         </is>
       </c>
       <c r="H289" s="5" t="n">
-        <v>-0.0138</v>
+        <v>-0.024371</v>
       </c>
       <c r="I289" s="5" t="n">
-        <v>-0.015</v>
+        <v>-0.035935</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -27795,14 +27707,10 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Royalty income</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -27819,10 +27727,10 @@
         </is>
       </c>
       <c r="H290" s="5" t="n">
-        <v>0.002771</v>
+        <v>-0.0138</v>
       </c>
       <c r="I290" s="5" t="n">
-        <v>0.002651</v>
+        <v>-0.015</v>
       </c>
       <c r="J290" t="inlineStr">
         <is>
@@ -27873,12 +27781,12 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Foreign Exchange</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>ForeignExchangeTradingGains</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -27897,10 +27805,10 @@
         </is>
       </c>
       <c r="H291" s="5" t="n">
-        <v>0.000829</v>
+        <v>0.002771</v>
       </c>
       <c r="I291" s="5" t="n">
-        <v>0.10098</v>
+        <v>0.002651</v>
       </c>
       <c r="J291" t="inlineStr">
         <is>
@@ -27951,10 +27859,14 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Loss on disposal of well-site equipment</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr"/>
+          <t>Foreign Exchange</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -27970,13 +27882,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H292" s="5" t="n">
+        <v>0.000829</v>
       </c>
       <c r="I292" s="5" t="n">
-        <v>-0.025845</v>
+        <v>0.10098</v>
       </c>
       <c r="J292" t="inlineStr">
         <is>
@@ -28027,7 +27937,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 7</t>
+          <t>Loss on disposal of well-site equipment</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -28046,11 +27956,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H293" s="5" t="n">
-        <v>0.347484</v>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I293" s="5" t="n">
-        <v>4.7e-05</v>
+        <v>-0.025845</v>
       </c>
       <c r="J293" t="inlineStr">
         <is>
@@ -28101,7 +28013,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Impairment of petroleum and natural gas exploration 8 assets</t>
+          <t>Impairment of exploration and evaluation assets 7</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -28121,12 +28033,10 @@
         </is>
       </c>
       <c r="H294" s="5" t="n">
-        <v>0.068102</v>
-      </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.347484</v>
+      </c>
+      <c r="I294" s="5" t="n">
+        <v>4.7e-05</v>
       </c>
       <c r="J294" t="inlineStr">
         <is>
@@ -28177,7 +28087,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Premium paid on acquisition of Petro One 3</t>
+          <t>Impairment of petroleum and natural gas exploration 8 assets</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
@@ -28197,7 +28107,7 @@
         </is>
       </c>
       <c r="H295" s="5" t="n">
-        <v>3.218116</v>
+        <v>0.068102</v>
       </c>
       <c r="I295" t="inlineStr">
         <is>
@@ -28253,7 +28163,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Settlement of flow-through share premium liabilities 10</t>
+          <t>Premium paid on acquisition of Petro One 3</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
@@ -28273,7 +28183,7 @@
         </is>
       </c>
       <c r="H296" s="5" t="n">
-        <v>-0.278954</v>
+        <v>3.218116</v>
       </c>
       <c r="I296" t="inlineStr">
         <is>
@@ -28329,7 +28239,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Adjustment to accrued liabilities</t>
+          <t>Settlement of flow-through share premium liabilities 10</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -28348,13 +28258,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I297" s="5" t="n">
-        <v>-0.201747</v>
+      <c r="H297" s="5" t="n">
+        <v>-0.278954</v>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
@@ -28405,7 +28315,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Other expenses (income) total</t>
+          <t>Adjustment to accrued liabilities</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -28424,11 +28334,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H298" s="5" t="n">
-        <v>3.320177</v>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I298" s="5" t="n">
-        <v>-0.174849</v>
+        <v>-0.201747</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -28479,14 +28391,10 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Other expenses (income) total</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -28503,10 +28411,10 @@
         </is>
       </c>
       <c r="H299" s="5" t="n">
-        <v>-5.341128</v>
+        <v>3.320177</v>
       </c>
       <c r="I299" s="5" t="n">
-        <v>-4.09181</v>
+        <v>-0.174849</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
@@ -28557,12 +28465,12 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted $</t>
+          <t>Net loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -28581,10 +28489,10 @@
         </is>
       </c>
       <c r="H300" s="5" t="n">
-        <v>-4e-08</v>
+        <v>-5.341128</v>
       </c>
       <c r="I300" s="5" t="n">
-        <v>-2e-08</v>
+        <v>-4.09181</v>
       </c>
       <c r="J300" t="inlineStr">
         <is>
@@ -28630,15 +28538,19 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Management consulting 12</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr"/>
+          <t>Loss per share, basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -28649,16 +28561,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G301" s="5" t="n">
-        <v>0.0171</v>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H301" s="5" t="n">
-        <v>0.059691</v>
-      </c>
-      <c r="I301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4e-08</v>
+      </c>
+      <c r="I301" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -28709,7 +28621,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Corporate development and communication 12</t>
+          <t>Management consulting 12</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -28724,10 +28636,10 @@
         </is>
       </c>
       <c r="G302" s="5" t="n">
-        <v>0.0356</v>
+        <v>0.0171</v>
       </c>
       <c r="H302" s="5" t="n">
-        <v>0.056935</v>
+        <v>0.059691</v>
       </c>
       <c r="I302" t="inlineStr">
         <is>
@@ -28783,14 +28695,10 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Office and miscellaneous 12</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Corporate development and communication 12</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -28802,10 +28710,10 @@
         </is>
       </c>
       <c r="G303" s="5" t="n">
-        <v>0.070392</v>
+        <v>0.0356</v>
       </c>
       <c r="H303" s="5" t="n">
-        <v>0.148932</v>
+        <v>0.056935</v>
       </c>
       <c r="I303" t="inlineStr">
         <is>
@@ -28861,12 +28769,12 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Professional fees 12</t>
+          <t>Office and miscellaneous 12</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -28880,10 +28788,10 @@
         </is>
       </c>
       <c r="G304" s="5" t="n">
-        <v>0.185492</v>
+        <v>0.070392</v>
       </c>
       <c r="H304" s="5" t="n">
-        <v>0.427974</v>
+        <v>0.148932</v>
       </c>
       <c r="I304" t="inlineStr">
         <is>
@@ -28939,12 +28847,12 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Rent 12</t>
+          <t>Professional fees 12</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -28958,10 +28866,10 @@
         </is>
       </c>
       <c r="G305" s="5" t="n">
-        <v>0.0594</v>
+        <v>0.185492</v>
       </c>
       <c r="H305" s="5" t="n">
-        <v>0.07425</v>
+        <v>0.427974</v>
       </c>
       <c r="I305" t="inlineStr">
         <is>
@@ -29017,10 +28925,14 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Stock-based compensation 11</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr"/>
+          <t>Rent 12</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -29032,10 +28944,10 @@
         </is>
       </c>
       <c r="G306" s="5" t="n">
-        <v>0.206338</v>
+        <v>0.0594</v>
       </c>
       <c r="H306" s="5" t="n">
-        <v>1.184008</v>
+        <v>0.07425</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -29086,12 +28998,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Accretion 14</t>
+          <t>Stock-based compensation 11</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
@@ -29105,13 +29017,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G307" s="5" t="n">
+        <v>0.206338</v>
       </c>
       <c r="H307" s="5" t="n">
-        <v>0.0026</v>
+        <v>1.184008</v>
       </c>
       <c r="I307" t="inlineStr">
         <is>
@@ -29167,14 +29077,10 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Amortization 7</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Accretion 14</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -29185,11 +29091,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G308" s="5" t="n">
-        <v>0.000934</v>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H308" s="5" t="n">
-        <v>0.002771</v>
+        <v>0.0026</v>
       </c>
       <c r="I308" t="inlineStr">
         <is>
@@ -29245,10 +29153,14 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Impairment of evaluation and exploration assets 8</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr"/>
+          <t>Amortization 7</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -29260,10 +29172,10 @@
         </is>
       </c>
       <c r="G309" s="5" t="n">
-        <v>0.615159</v>
+        <v>0.000934</v>
       </c>
       <c r="H309" s="5" t="n">
-        <v>0.347484</v>
+        <v>0.002771</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
@@ -29319,7 +29231,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Impairment of petroleum and natural gas exploration assets 9</t>
+          <t>Impairment of evaluation and exploration assets 8</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -29334,10 +29246,10 @@
         </is>
       </c>
       <c r="G310" s="5" t="n">
-        <v>0.081613</v>
+        <v>0.615159</v>
       </c>
       <c r="H310" s="5" t="n">
-        <v>0.068102</v>
+        <v>0.347484</v>
       </c>
       <c r="I310" t="inlineStr">
         <is>
@@ -29393,7 +29305,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Premium paid on acquisition of Petro One 3</t>
+          <t>Impairment of petroleum and natural gas exploration assets 9</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
@@ -29407,13 +29319,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G311" s="5" t="n">
+        <v>0.081613</v>
       </c>
       <c r="H311" s="5" t="n">
-        <v>3.218116</v>
+        <v>0.068102</v>
       </c>
       <c r="I311" t="inlineStr">
         <is>
@@ -29469,7 +29379,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Settlement of flow-through share premium liabilities 11</t>
+          <t>Premium paid on acquisition of Petro One 3</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -29483,11 +29393,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G312" s="5" t="n">
-        <v>-0.076185</v>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H312" s="5" t="n">
-        <v>-0.278954</v>
+        <v>3.218116</v>
       </c>
       <c r="I312" t="inlineStr">
         <is>
@@ -29543,14 +29455,10 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Settlement of flow-through share premium liabilities 11</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -29562,10 +29470,10 @@
         </is>
       </c>
       <c r="G313" s="5" t="n">
-        <v>-1.269843</v>
+        <v>-0.076185</v>
       </c>
       <c r="H313" s="5" t="n">
-        <v>-5.341128</v>
+        <v>-0.278954</v>
       </c>
       <c r="I313" t="inlineStr">
         <is>
@@ -29621,25 +29529,29 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted $</t>
+          <t>Net and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E314" s="5" t="n">
-        <v>-1.5e-07</v>
-      </c>
-      <c r="F314" s="5" t="n">
-        <v>-2.5e-08</v>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G314" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-1.269843</v>
       </c>
       <c r="H314" s="5" t="n">
-        <v>-4e-08</v>
+        <v>-5.341128</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
@@ -29690,30 +29602,30 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Management consulting 9</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss per share, basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E315" s="5" t="n">
+        <v>-1.5e-07</v>
       </c>
       <c r="F315" s="5" t="n">
-        <v>0.0375</v>
+        <v>-2.5e-08</v>
       </c>
       <c r="G315" s="5" t="n">
-        <v>0.0171</v>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="H315" s="5" t="n">
+        <v>-4e-08</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
@@ -29769,26 +29681,20 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Consulting fees 9</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Management consulting 9</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F316" s="5" t="n">
+        <v>0.0375</v>
       </c>
       <c r="G316" s="5" t="n">
-        <v>0.06</v>
+        <v>0.0171</v>
       </c>
       <c r="H316" t="inlineStr">
         <is>
@@ -29849,20 +29755,26 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Corporate development and communication 9</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr"/>
+          <t>Consulting fees 9</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F317" s="5" t="n">
-        <v>0.055767</v>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G317" s="5" t="n">
-        <v>0.0356</v>
+        <v>0.06</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
@@ -29923,24 +29835,20 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Office and miscellaneous 9</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Corporate development and communication 9</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F318" s="5" t="n">
-        <v>0.06582300000000001</v>
+        <v>0.055767</v>
       </c>
       <c r="G318" s="5" t="n">
-        <v>0.070392</v>
+        <v>0.0356</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
@@ -30001,12 +29909,12 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Professional fees 9</t>
+          <t>Office and miscellaneous 9</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -30015,10 +29923,10 @@
         </is>
       </c>
       <c r="F319" s="5" t="n">
-        <v>0.132863</v>
+        <v>0.06582300000000001</v>
       </c>
       <c r="G319" s="5" t="n">
-        <v>0.185492</v>
+        <v>0.070392</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
@@ -30079,22 +29987,24 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Property investigation fee</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr"/>
+          <t>Professional fees 9</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F320" s="5" t="n">
-        <v>0.0095</v>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.132863</v>
+      </c>
+      <c r="G320" s="5" t="n">
+        <v>0.185492</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
@@ -30155,24 +30065,22 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Rent 9</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Property investigation fee</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F321" s="5" t="n">
-        <v>0.0594</v>
-      </c>
-      <c r="G321" s="5" t="n">
-        <v>0.0594</v>
+        <v>0.0095</v>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
@@ -30233,20 +30141,24 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Stock-based compensation 8</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr"/>
+          <t>Rent 9</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F322" s="5" t="n">
-        <v>0.449548</v>
+        <v>0.0594</v>
       </c>
       <c r="G322" s="5" t="n">
-        <v>0.206338</v>
+        <v>0.0594</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
@@ -30302,27 +30214,25 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Amortization 4</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E323" s="5" t="n">
-        <v>0.003513</v>
+          <t>Stock-based compensation 8</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F323" s="5" t="n">
-        <v>0.002039</v>
+        <v>0.449548</v>
       </c>
       <c r="G323" s="5" t="n">
-        <v>0.000934</v>
+        <v>0.206338</v>
       </c>
       <c r="H323" t="inlineStr">
         <is>
@@ -30383,26 +30293,22 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Realized gain from foreign exchange</t>
+          <t>Amortization 4</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>ForeignExchangeTradingGains</t>
-        </is>
-      </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E324" s="5" t="n">
+        <v>0.003513</v>
+      </c>
+      <c r="F324" s="5" t="n">
+        <v>0.002039</v>
       </c>
       <c r="G324" s="5" t="n">
-        <v>-0.013883</v>
+        <v>0.000934</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
@@ -30458,25 +30364,31 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 5</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr"/>
+          <t>Realized gain from foreign exchange</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F325" s="5" t="n">
-        <v>0.983423</v>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G325" s="5" t="n">
-        <v>0.696774</v>
+        <v>-0.013883</v>
       </c>
       <c r="H325" t="inlineStr">
         <is>
@@ -30532,12 +30444,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Settlement of flow-through share premium</t>
+          <t>Impairment of exploration and evaluation</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Settlement of flow-through share premium liabilities 8</t>
+          <t>Impairment of exploration and evaluation assets 5</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
@@ -30546,13 +30458,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F326" s="5" t="n">
+        <v>0.983423</v>
       </c>
       <c r="G326" s="5" t="n">
-        <v>-0.076185</v>
+        <v>0.696774</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
@@ -30613,7 +30523,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Settlement of flow-through share premium total</t>
+          <t>Settlement of flow-through share premium liabilities 8</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
@@ -30622,11 +30532,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F327" s="5" t="n">
-        <v>-0.980561</v>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G327" s="5" t="n">
-        <v>-0.604635</v>
+        <v>-0.076185</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
@@ -30687,24 +30599,20 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Settlement of flow-through share premium total</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F328" s="5" t="n">
-        <v>-1.830197</v>
+        <v>-0.980561</v>
       </c>
       <c r="G328" s="5" t="n">
-        <v>-1.269843</v>
+        <v>-0.604635</v>
       </c>
       <c r="H328" t="inlineStr">
         <is>
@@ -30765,12 +30673,12 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted $</t>
+          <t>Net and comprehensive loss $</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -30779,10 +30687,10 @@
         </is>
       </c>
       <c r="F329" s="5" t="n">
-        <v>-2.5e-08</v>
+        <v>-1.830197</v>
       </c>
       <c r="G329" s="5" t="n">
-        <v>-1.3e-08</v>
+        <v>-1.269843</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
@@ -30836,23 +30744,31 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr"/>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Settlement of flow-through share premium</t>
+        </is>
+      </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Note December 31, 2014 December</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr"/>
-      <c r="E330" s="5" t="n">
-        <v>0.002013</v>
+          <t>Loss per share, basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F330" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.5e-08</v>
+      </c>
+      <c r="G330" s="5" t="n">
+        <v>-1.3e-08</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
@@ -30906,22 +30822,18 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B331" t="inlineStr"/>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Management consulting 8</t>
+          <t>Note December 31, 2014 December</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
       <c r="E331" s="5" t="n">
-        <v>0.03625</v>
+        <v>0.002013</v>
       </c>
       <c r="F331" s="5" t="n">
-        <v>0.0375</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
@@ -30987,15 +30899,15 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Corporate development and communication 8</t>
+          <t>Management consulting 8</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
       <c r="E332" s="5" t="n">
-        <v>0.06</v>
+        <v>0.03625</v>
       </c>
       <c r="F332" s="5" t="n">
-        <v>0.055767</v>
+        <v>0.0375</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
@@ -31061,19 +30973,15 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Office and miscellaneous 8</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Corporate development and communication 8</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" s="5" t="n">
-        <v>0.072784</v>
+        <v>0.06</v>
       </c>
       <c r="F333" s="5" t="n">
-        <v>0.06582300000000001</v>
+        <v>0.055767</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
@@ -31139,19 +31047,19 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Professional fees 8</t>
+          <t>Office and miscellaneous 8</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E334" s="5" t="n">
-        <v>0.170242</v>
+        <v>0.072784</v>
       </c>
       <c r="F334" s="5" t="n">
-        <v>0.132863</v>
+        <v>0.06582300000000001</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
@@ -31217,17 +31125,19 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Property investigation fees</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional fees 8</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E335" s="5" t="n">
+        <v>0.170242</v>
       </c>
       <c r="F335" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.132863</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
@@ -31293,19 +31203,17 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Rent 8</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E336" s="5" t="n">
-        <v>0.0594</v>
+          <t>Property investigation fees</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F336" s="5" t="n">
-        <v>0.0594</v>
+        <v>0.0095</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
@@ -31371,15 +31279,19 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Stock-based compensation 7</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr"/>
+          <t>Rent 8</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E337" s="5" t="n">
-        <v>0.117562</v>
+        <v>0.0594</v>
       </c>
       <c r="F337" s="5" t="n">
-        <v>0.449548</v>
+        <v>0.0594</v>
       </c>
       <c r="G337" t="inlineStr">
         <is>
@@ -31440,24 +31352,20 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Stock-based compensation 7</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" s="5" t="n">
-        <v>-10.018537</v>
+        <v>0.117562</v>
       </c>
       <c r="F338" s="5" t="n">
-        <v>-1.830197</v>
+        <v>0.449548</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
@@ -31518,20 +31426,24 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>See accompanying notes to the financial statements                                        4</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Total 14,635,115 (10,018,537) 397,220 2,502,777 134,927 117,562 7,769,064 (1,830,197) 74,221 189,305 449,548</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr"/>
+          <t>Net and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E339" s="5" t="n">
-        <v>5e-06</v>
+        <v>-10.018537</v>
       </c>
       <c r="F339" s="5" t="n">
-        <v>6.651941</v>
+        <v>-1.830197</v>
       </c>
       <c r="G339" t="inlineStr">
         <is>
@@ -31597,15 +31509,15 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>- - - - (1,830,197) - - - Deficit (24,615,286) (10,018,537)</t>
+          <t>Total 14,635,115 (10,018,537) 397,220 2,502,777 134,927 117,562 7,769,064 (1,830,197) 74,221 189,305 449,548</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
       <c r="E340" s="5" t="n">
-        <v>-36.46402</v>
+        <v>5e-06</v>
       </c>
       <c r="F340" s="5" t="n">
-        <v>-34.633823</v>
+        <v>6.651941</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
@@ -31671,19 +31583,15 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>reserve    12,130,589 - - -  134,927  117,562    12,383,078 - - -  449,548    12,832,626                                                                                Share-based                                                           payment $             $ to - - - - - - - -</t>
+          <t>- - - - (1,830,197) - - - Deficit (24,615,286) (10,018,537)</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E341" s="5" t="n">
+        <v>-36.46402</v>
+      </c>
+      <c r="F341" s="5" t="n">
+        <v>-34.633823</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
@@ -31749,15 +31657,19 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>shares</t>
+          <t>reserve    12,130,589 - - -  134,927  117,562    12,383,078 - - -  449,548    12,832,626                                                                                Share-based                                                           payment $             $ to - - - - - - - -</t>
         </is>
       </c>
       <c r="D342" t="inlineStr"/>
-      <c r="E342" s="5" t="n">
-        <v>-0.124985</v>
-      </c>
-      <c r="F342" s="5" t="n">
-        <v>0.124985</v>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
@@ -31818,71 +31730,145 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
+          <t>See accompanying notes to the financial statements                                        4</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>shares</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" s="5" t="n">
+        <v>-0.124985</v>
+      </c>
+      <c r="F343" s="5" t="n">
+        <v>0.124985</v>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
           <t>capital</t>
         </is>
       </c>
-      <c r="C343" t="inlineStr">
+      <c r="C344" t="inlineStr">
         <is>
           <t>capital   $             $</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P343" t="inlineStr">
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
         <is>
           <t>-</t>
         </is>
